--- a/shot-grid-frontend/docs/镜头-样表.xlsx
+++ b/shot-grid-frontend/docs/镜头-样表.xlsx
@@ -9,14 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13335" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="14055"/>
   </bookViews>
   <sheets>
     <sheet name="EP001" sheetId="1" r:id="rId1"/>
     <sheet name="EP002" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'EP001'!$A$1:$P$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'EP001'!$A$1:$O$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="77">
   <si>
     <t>场次</t>
   </si>
@@ -47,63 +47,60 @@
     <t>时长(s)</t>
   </si>
   <si>
+    <t>镜头缩略图</t>
+  </si>
+  <si>
+    <t>制作内容描述</t>
+  </si>
+  <si>
+    <t>景别</t>
+  </si>
+  <si>
+    <t>机位</t>
+  </si>
+  <si>
+    <t>镜头运动</t>
+  </si>
+  <si>
+    <t>焦段(mm)</t>
+  </si>
+  <si>
+    <t>场景</t>
+  </si>
+  <si>
+    <t>台词/对白</t>
+  </si>
+  <si>
+    <t>音效</t>
+  </si>
+  <si>
+    <t>色调参考</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>镜头状态</t>
+  </si>
+  <si>
+    <t>分镜</t>
+  </si>
+  <si>
+    <t>视频</t>
+  </si>
+  <si>
+    <t>反馈</t>
+  </si>
+  <si>
     <t>制作人</t>
   </si>
   <si>
-    <t>镜头缩略图</t>
-  </si>
-  <si>
-    <t>制作内容描述</t>
-  </si>
-  <si>
-    <t>景别</t>
-  </si>
-  <si>
-    <t>机位</t>
-  </si>
-  <si>
-    <t>镜头运动</t>
-  </si>
-  <si>
-    <t>焦段(mm)</t>
-  </si>
-  <si>
-    <t>场景</t>
-  </si>
-  <si>
-    <t>台词/对白</t>
-  </si>
-  <si>
-    <t>音效</t>
-  </si>
-  <si>
-    <t>色调参考</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>镜头状态</t>
-  </si>
-  <si>
-    <t>分镜</t>
-  </si>
-  <si>
-    <t>视频</t>
-  </si>
-  <si>
-    <t>反馈</t>
-  </si>
-  <si>
     <t>序</t>
   </si>
   <si>
     <t>S001</t>
   </si>
   <si>
-    <t>晓亮</t>
-  </si>
-  <si>
     <t>NoMud号漂浮于宇宙,飞船4/5侧对镜头</t>
   </si>
   <si>
@@ -131,120 +128,105 @@
     <t>01场</t>
   </si>
   <si>
+    <t>稍带斜角度拍门上贴纸：“禁止入内”“内有恶犬”</t>
+  </si>
+  <si>
+    <t>特写</t>
+  </si>
+  <si>
+    <t>手持呼吸感</t>
+  </si>
+  <si>
+    <t>翱天室内</t>
+  </si>
+  <si>
+    <t>轻微电流声，以及金属板偶尔轻微变形的声音</t>
+  </si>
+  <si>
+    <t>暖色顶光，主光为硬光，但经过舱体金属折射，暗部不是死黑</t>
+  </si>
+  <si>
+    <t>需要比较好的画面重心表现，用较浅的景深去收拾视觉中心表达。</t>
+  </si>
+  <si>
     <t>S002</t>
   </si>
   <si>
-    <t>稍带斜角度拍门上贴纸：“禁止入内”“内有恶犬”</t>
-  </si>
-  <si>
-    <t>特写</t>
-  </si>
-  <si>
-    <t>手持呼吸感</t>
-  </si>
-  <si>
-    <t>翱天室内</t>
-  </si>
-  <si>
-    <t>轻微电流声，以及金属板偶尔轻微变形的声音</t>
-  </si>
-  <si>
-    <t>暖色顶光，主光为硬光，但经过舱体金属折射，暗部不是死黑</t>
-  </si>
-  <si>
-    <t>需要比较好的画面重心表现，用较浅的景深去收拾视觉中心表达。</t>
+    <t>同上一镜角度拍舱门，突然船体一晃，门“吱呀”一声被晃开。</t>
+  </si>
+  <si>
+    <t>中景</t>
+  </si>
+  <si>
+    <t>手持呼吸感，猛地一晃</t>
+  </si>
+  <si>
+    <t>35/25</t>
+  </si>
+  <si>
+    <t>轻微电流声，以及金属板偶尔轻微变形的声音。门被晃开的吱呀声。</t>
+  </si>
+  <si>
+    <t>用镜头变形表现出舱室走廊的狭小逼仄</t>
   </si>
   <si>
     <t>S003</t>
   </si>
   <si>
-    <t>同上一镜角度拍舱门，突然船体一晃，门“吱呀”一声被晃开。</t>
-  </si>
-  <si>
-    <t>中景</t>
-  </si>
-  <si>
-    <t>手持呼吸感，猛地一晃</t>
-  </si>
-  <si>
-    <t>35/25</t>
-  </si>
-  <si>
-    <t>轻微电流声，以及金属板偶尔轻微变形的声音。门被晃开的吱呀声。</t>
-  </si>
-  <si>
-    <t>用镜头变形表现出舱室走廊的狭小逼仄</t>
+    <t>门撞到同样斑驳的铁皮墙上，发出一声巨响，门冲镜而来，砸在镜头上震动感</t>
+  </si>
+  <si>
+    <t>近景</t>
+  </si>
+  <si>
+    <t>低机位稍仰</t>
+  </si>
+  <si>
+    <t>手持呼吸感，冲镜震动</t>
+  </si>
+  <si>
+    <t>24/18</t>
+  </si>
+  <si>
+    <t>铁门撞墙巨响</t>
+  </si>
+  <si>
+    <t>02场</t>
+  </si>
+  <si>
+    <t>一组苟翱天走在走廊上哼着歌扭动的蒙太奇</t>
+  </si>
+  <si>
+    <t>远中近</t>
+  </si>
+  <si>
+    <t>NoMud号走廊</t>
+  </si>
+  <si>
+    <t>侧拍他唱着歌一个滑步，滑过走廊转角。</t>
+  </si>
+  <si>
+    <t>小全</t>
+  </si>
+  <si>
+    <t>平视</t>
+  </si>
+  <si>
+    <t>固定</t>
+  </si>
+  <si>
+    <t>正面拍摄他滑过走廊转角，视线被前面的东西吸引</t>
+  </si>
+  <si>
+    <t>跟拍</t>
+  </si>
+  <si>
+    <t>杀……人……啦</t>
   </si>
   <si>
     <t>S004</t>
   </si>
   <si>
-    <t>门撞到同样斑驳的铁皮墙上，发出一声巨响，门冲镜而来，砸在镜头上震动感</t>
-  </si>
-  <si>
-    <t>近景</t>
-  </si>
-  <si>
-    <t>低机位稍仰</t>
-  </si>
-  <si>
-    <t>手持呼吸感，冲镜震动</t>
-  </si>
-  <si>
-    <t>24/18</t>
-  </si>
-  <si>
-    <t>铁门撞墙巨响</t>
-  </si>
-  <si>
-    <t>02场</t>
-  </si>
-  <si>
-    <t>S005</t>
-  </si>
-  <si>
-    <t>春霞</t>
-  </si>
-  <si>
-    <t>一组苟翱天走在走廊上哼着歌扭动的蒙太奇</t>
-  </si>
-  <si>
-    <t>远中近</t>
-  </si>
-  <si>
-    <t>NoMud号走廊</t>
-  </si>
-  <si>
-    <t>S006</t>
-  </si>
-  <si>
-    <t>侧拍他唱着歌一个滑步，滑过走廊转角。</t>
-  </si>
-  <si>
-    <t>小全</t>
-  </si>
-  <si>
-    <t>平视</t>
-  </si>
-  <si>
-    <t>固定</t>
-  </si>
-  <si>
-    <t>S007</t>
-  </si>
-  <si>
-    <t>正面拍摄他滑过走廊转角，视线被前面的东西吸引</t>
-  </si>
-  <si>
-    <t>跟拍</t>
-  </si>
-  <si>
-    <t>杀……人……啦</t>
-  </si>
-  <si>
-    <t>S008</t>
-  </si>
-  <si>
     <t>走廊尽头的动力舱门外，一个被脏抹布盖住摄像头的清洁机器人在原地转着圈圈，一字一顿地说着</t>
   </si>
   <si>
@@ -260,21 +242,12 @@
     <t>03场</t>
   </si>
   <si>
-    <t>S009</t>
-  </si>
-  <si>
-    <t>嘉璋</t>
-  </si>
-  <si>
     <t>贴满 "维修中 高压危险" 的舱门空镜，门缝里透出忽明忽暗的光。带一点角度。</t>
   </si>
   <si>
     <t>走廊</t>
   </si>
   <si>
-    <t>S010</t>
-  </si>
-  <si>
     <t>带一点侧角度拍苟翱天从右入画，小心翼翼地趴在门缝上往里看。</t>
   </si>
   <si>
@@ -284,16 +257,10 @@
     <t>救……命……</t>
   </si>
   <si>
-    <t>S011</t>
-  </si>
-  <si>
     <t>对着脸拍，带镜头畸变，苟翱天立刻把耳朵贴到门缝仔细听，嘴里小声喊着。</t>
   </si>
   <si>
     <t>有人吗？王胖子？大胡子？你们还活着吗？</t>
-  </si>
-  <si>
-    <t>S012</t>
   </si>
   <si>
     <t>从苟翱天侧后拍他被凄厉的惨叫吓得从舱门弹开。</t>
@@ -1323,29 +1290,28 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AK13"/>
+  <dimension ref="A1:AJ13"/>
   <sheetFormatPr defaultColWidth="12" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.375" customWidth="1"/>
     <col min="2" max="2" width="15.375" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="31" customWidth="1"/>
-    <col min="7" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="23" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="18.375" customWidth="1"/>
-    <col min="15" max="15" width="23.375" customWidth="1"/>
-    <col min="16" max="16" width="31.125" customWidth="1"/>
-    <col min="17" max="17" width="30" customWidth="1"/>
-    <col min="18" max="18" width="28" customWidth="1"/>
-    <col min="19" max="37" width="12" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="31" customWidth="1"/>
+    <col min="6" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="23" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="18.375" customWidth="1"/>
+    <col min="14" max="14" width="23.375" customWidth="1"/>
+    <col min="15" max="15" width="31.125" customWidth="1"/>
+    <col min="16" max="16" width="30" customWidth="1"/>
+    <col min="17" max="17" width="28" customWidth="1"/>
+    <col min="18" max="36" width="12" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:37">
+    <row r="1" ht="25" customHeight="1" spans="1:36">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1391,11 +1357,11 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
       <c r="S1" s="3" t="s">
         <v>16</v>
       </c>
@@ -1405,8 +1371,8 @@
       <c r="U1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="3" t="s">
-        <v>3</v>
+      <c r="W1" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="X1" s="3" t="s">
         <v>16</v>
@@ -1417,8 +1383,8 @@
       <c r="Z1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="AA1" s="3" t="s">
-        <v>3</v>
+      <c r="AB1" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="AC1" s="3" t="s">
         <v>16</v>
@@ -1429,8 +1395,8 @@
       <c r="AE1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="AF1" s="3" t="s">
-        <v>3</v>
+      <c r="AG1" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="AH1" s="3" t="s">
         <v>16</v>
@@ -1441,11 +1407,8 @@
       <c r="AJ1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="AK1" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" ht="71" customHeight="1" spans="1:37">
+    </row>
+    <row r="2" ht="71" customHeight="1" spans="1:36">
       <c r="A2" s="4" t="s">
         <v>19</v>
       </c>
@@ -1455,10 +1418,10 @@
       <c r="C2" s="4">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="4"/>
+      <c r="E2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="4"/>
       <c r="F2" s="4" t="s">
         <v>22</v>
       </c>
@@ -1468,479 +1431,443 @@
       <c r="H2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="4">
+        <v>135</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="J2" s="4">
-        <v>135</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="4"/>
+      <c r="M2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="4"/>
       <c r="N2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="5"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+    </row>
+    <row r="3" ht="71" customHeight="1" spans="1:36">
+      <c r="A3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-    </row>
-    <row r="3" ht="71" customHeight="1" spans="1:37">
-      <c r="A3" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="B3" s="4" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C3" s="4">
         <v>1.5</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="F3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="I3" s="4">
+        <v>85</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="K3" s="4"/>
+      <c r="L3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="4">
-        <v>85</v>
-      </c>
-      <c r="K3" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="O3" s="5"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+    </row>
+    <row r="4" ht="71" customHeight="1" spans="1:36">
+      <c r="A4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-    </row>
-    <row r="4" ht="71" customHeight="1" spans="1:37">
-      <c r="A4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>39</v>
       </c>
       <c r="C4" s="4">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="F4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="M4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4" t="s">
+      <c r="O4" s="5"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+    </row>
+    <row r="5" ht="71" customHeight="1" spans="1:36">
+      <c r="A5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-    </row>
-    <row r="5" ht="71" customHeight="1" spans="1:37">
-      <c r="A5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="C5" s="4">
         <v>1</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="F5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="M5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+    </row>
+    <row r="6" ht="71" customHeight="1" spans="1:36">
+      <c r="A6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="O5" s="4"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-    </row>
-    <row r="6" ht="71" customHeight="1" spans="1:37">
-      <c r="A6" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="B6" s="4" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="C6" s="4">
         <v>10</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="F6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4" t="s">
-        <v>58</v>
-      </c>
+      <c r="J6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-    </row>
-    <row r="7" ht="71" customHeight="1" spans="1:37">
+    </row>
+    <row r="7" ht="71" customHeight="1" spans="1:36">
       <c r="A7" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="C7" s="4">
         <v>2</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="4"/>
+      <c r="E7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="4"/>
       <c r="F7" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4" t="s">
         <v>58</v>
       </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-    </row>
-    <row r="8" ht="71" customHeight="1" spans="1:37">
+    </row>
+    <row r="8" ht="71" customHeight="1" spans="1:36">
       <c r="A8" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="C8" s="4">
         <v>1</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="F8" s="4" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="J8" s="4"/>
+        <v>60</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="K8" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>67</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-    </row>
-    <row r="9" ht="71" customHeight="1" spans="1:37">
+    </row>
+    <row r="9" ht="71" customHeight="1" spans="1:36">
       <c r="A9" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C9" s="4">
         <v>3</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="F9" s="4" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="J9" s="4"/>
+        <v>65</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="K9" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>72</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-    </row>
-    <row r="10" ht="71" customHeight="1" spans="1:37">
+    </row>
+    <row r="10" ht="71" customHeight="1" spans="1:36">
       <c r="A10" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="C10" s="4">
         <v>1</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="F10" s="4" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4" t="s">
-        <v>77</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="6"/>
       <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-    </row>
-    <row r="11" ht="71" customHeight="1" spans="1:37">
+    </row>
+    <row r="11" ht="71" customHeight="1" spans="1:36">
       <c r="A11" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="C11" s="4">
         <v>3</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="F11" s="4" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J11" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="K11" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>81</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="6"/>
       <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
-    </row>
-    <row r="12" ht="71" customHeight="1" spans="1:37">
+    </row>
+    <row r="12" ht="71" customHeight="1" spans="1:36">
       <c r="A12" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="C12" s="4">
         <v>6</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>73</v>
+      </c>
       <c r="F12" s="4" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J12" s="4">
+        <v>32</v>
+      </c>
+      <c r="I12" s="4">
         <v>28</v>
       </c>
+      <c r="J12" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="K12" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>84</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-    </row>
-    <row r="13" ht="71" customHeight="1" spans="1:37">
+    </row>
+    <row r="13" ht="71" customHeight="1" spans="1:36">
       <c r="A13" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="C13" s="4">
         <v>2</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="4"/>
+      <c r="E13" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="4"/>
       <c r="F13" s="4" t="s">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J13" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="K13" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>87</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P13" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O13" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1951,29 +1878,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK13"/>
+  <dimension ref="A1:AJ13"/>
   <sheetFormatPr defaultColWidth="12" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.375" customWidth="1"/>
     <col min="2" max="2" width="15.375" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="31" customWidth="1"/>
-    <col min="7" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="23" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="18.375" customWidth="1"/>
-    <col min="15" max="15" width="23.375" customWidth="1"/>
-    <col min="16" max="16" width="31.125" customWidth="1"/>
-    <col min="17" max="17" width="30" customWidth="1"/>
-    <col min="18" max="18" width="28" customWidth="1"/>
-    <col min="19" max="37" width="12" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="31" customWidth="1"/>
+    <col min="6" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="23" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="18.375" customWidth="1"/>
+    <col min="14" max="14" width="23.375" customWidth="1"/>
+    <col min="15" max="15" width="31.125" customWidth="1"/>
+    <col min="16" max="16" width="30" customWidth="1"/>
+    <col min="17" max="17" width="28" customWidth="1"/>
+    <col min="18" max="36" width="12" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="25" customHeight="1" spans="1:37">
+    <row r="1" customFormat="1" ht="25" customHeight="1" spans="1:36">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2019,11 +1945,11 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
       <c r="S1" s="3" t="s">
         <v>16</v>
       </c>
@@ -2033,10 +1959,10 @@
       <c r="U1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W1"/>
+      <c r="V1"/>
+      <c r="W1" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="X1" s="3" t="s">
         <v>16</v>
       </c>
@@ -2046,10 +1972,10 @@
       <c r="Z1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="AA1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB1"/>
+      <c r="AA1"/>
+      <c r="AB1" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="AC1" s="3" t="s">
         <v>16</v>
       </c>
@@ -2059,10 +1985,10 @@
       <c r="AE1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="AF1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG1"/>
+      <c r="AF1"/>
+      <c r="AG1" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="AH1" s="3" t="s">
         <v>16</v>
       </c>
@@ -2072,11 +1998,8 @@
       <c r="AJ1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="AK1" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" customFormat="1" ht="71" customHeight="1" spans="1:37">
+    </row>
+    <row r="2" customFormat="1" ht="71" customHeight="1" spans="1:36">
       <c r="A2" s="4" t="s">
         <v>19</v>
       </c>
@@ -2086,10 +2009,10 @@
       <c r="C2" s="4">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="4"/>
+      <c r="E2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="4"/>
       <c r="F2" s="4" t="s">
         <v>22</v>
       </c>
@@ -2099,476 +2022,440 @@
       <c r="H2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="4">
+        <v>135</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="J2" s="4">
-        <v>135</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="4"/>
+      <c r="M2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="4"/>
       <c r="N2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="5"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+    </row>
+    <row r="3" customFormat="1" ht="71" customHeight="1" spans="1:36">
+      <c r="A3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-    </row>
-    <row r="3" customFormat="1" ht="71" customHeight="1" spans="1:37">
-      <c r="A3" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="B3" s="4" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C3" s="4">
         <v>1.5</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="F3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="I3" s="4">
+        <v>85</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="K3" s="4"/>
+      <c r="L3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="4">
-        <v>85</v>
-      </c>
-      <c r="K3" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="O3" s="5"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+    </row>
+    <row r="4" customFormat="1" ht="71" customHeight="1" spans="1:36">
+      <c r="A4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-    </row>
-    <row r="4" customFormat="1" ht="71" customHeight="1" spans="1:37">
-      <c r="A4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>39</v>
       </c>
       <c r="C4" s="4">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="F4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="M4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4" t="s">
+      <c r="O4" s="5"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+    </row>
+    <row r="5" customFormat="1" ht="71" customHeight="1" spans="1:36">
+      <c r="A5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-    </row>
-    <row r="5" customFormat="1" ht="71" customHeight="1" spans="1:37">
-      <c r="A5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="C5" s="4">
         <v>1</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="F5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="M5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+    </row>
+    <row r="6" customFormat="1" ht="71" customHeight="1" spans="1:36">
+      <c r="A6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="O5" s="4"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-    </row>
-    <row r="6" customFormat="1" ht="71" customHeight="1" spans="1:37">
-      <c r="A6" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="B6" s="4" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="C6" s="4">
         <v>10</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="F6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4" t="s">
-        <v>58</v>
-      </c>
+      <c r="J6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-    </row>
-    <row r="7" customFormat="1" ht="71" customHeight="1" spans="1:37">
+    </row>
+    <row r="7" customFormat="1" ht="71" customHeight="1" spans="1:36">
       <c r="A7" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="C7" s="4">
         <v>2</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="4"/>
+      <c r="E7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="4"/>
       <c r="F7" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4" t="s">
         <v>58</v>
       </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-    </row>
-    <row r="8" customFormat="1" ht="71" customHeight="1" spans="1:37">
+    </row>
+    <row r="8" customFormat="1" ht="71" customHeight="1" spans="1:36">
       <c r="A8" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="C8" s="4">
         <v>1</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="F8" s="4" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="J8" s="4"/>
+        <v>60</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="K8" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>67</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-    </row>
-    <row r="9" customFormat="1" ht="71" customHeight="1" spans="1:37">
+    </row>
+    <row r="9" customFormat="1" ht="71" customHeight="1" spans="1:36">
       <c r="A9" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C9" s="4">
         <v>3</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="F9" s="4" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="J9" s="4"/>
+        <v>65</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="K9" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>72</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-    </row>
-    <row r="10" customFormat="1" ht="71" customHeight="1" spans="1:37">
+    </row>
+    <row r="10" customFormat="1" ht="71" customHeight="1" spans="1:36">
       <c r="A10" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="C10" s="4">
         <v>1</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="F10" s="4" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4" t="s">
-        <v>77</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="6"/>
       <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-    </row>
-    <row r="11" customFormat="1" ht="71" customHeight="1" spans="1:37">
+    </row>
+    <row r="11" customFormat="1" ht="71" customHeight="1" spans="1:36">
       <c r="A11" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="C11" s="4">
         <v>3</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="F11" s="4" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J11" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="K11" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>81</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="6"/>
       <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
-    </row>
-    <row r="12" customFormat="1" ht="71" customHeight="1" spans="1:37">
+    </row>
+    <row r="12" customFormat="1" ht="71" customHeight="1" spans="1:36">
       <c r="A12" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="C12" s="4">
         <v>6</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>73</v>
+      </c>
       <c r="F12" s="4" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J12" s="4">
+        <v>32</v>
+      </c>
+      <c r="I12" s="4">
         <v>28</v>
       </c>
+      <c r="J12" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="K12" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>84</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-    </row>
-    <row r="13" customFormat="1" ht="71" customHeight="1" spans="1:37">
+    </row>
+    <row r="13" customFormat="1" ht="71" customHeight="1" spans="1:36">
       <c r="A13" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="C13" s="4">
         <v>2</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="4"/>
+      <c r="E13" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="4"/>
       <c r="F13" s="4" t="s">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J13" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="K13" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>87</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/shot-grid-frontend/docs/镜头-样表.xlsx
+++ b/shot-grid-frontend/docs/镜头-样表.xlsx
@@ -98,7 +98,7 @@
     <t>序</t>
   </si>
   <si>
-    <t>S001</t>
+    <t>0001</t>
   </si>
   <si>
     <t>NoMud号漂浮于宇宙,飞船4/5侧对镜头</t>
@@ -149,7 +149,7 @@
     <t>需要比较好的画面重心表现，用较浅的景深去收拾视觉中心表达。</t>
   </si>
   <si>
-    <t>S002</t>
+    <t>0002</t>
   </si>
   <si>
     <t>同上一镜角度拍舱门，突然船体一晃，门“吱呀”一声被晃开。</t>
@@ -170,7 +170,7 @@
     <t>用镜头变形表现出舱室走廊的狭小逼仄</t>
   </si>
   <si>
-    <t>S003</t>
+    <t>0003</t>
   </si>
   <si>
     <t>门撞到同样斑驳的铁皮墙上，发出一声巨响，门冲镜而来，砸在镜头上震动感</t>
@@ -224,7 +224,7 @@
     <t>杀……人……啦</t>
   </si>
   <si>
-    <t>S004</t>
+    <t>0004</t>
   </si>
   <si>
     <t>走廊尽头的动力舱门外，一个被脏抹布盖住摄像头的清洁机器人在原地转着圈圈，一字一顿地说着</t>
@@ -968,6 +968,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1412,7 +1415,7 @@
       <c r="A2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="4">
@@ -1455,7 +1458,7 @@
       <c r="A3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C3" s="4">
@@ -1498,7 +1501,7 @@
       <c r="A4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C4" s="4">
@@ -1541,7 +1544,7 @@
       <c r="A5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="7" t="s">
         <v>44</v>
       </c>
       <c r="C5" s="4">
@@ -1582,7 +1585,7 @@
       <c r="A6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="4">
@@ -1613,7 +1616,7 @@
       <c r="A7" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C7" s="4">
@@ -1648,7 +1651,7 @@
       <c r="A8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="7" t="s">
         <v>44</v>
       </c>
       <c r="C8" s="4">
@@ -1685,7 +1688,7 @@
       <c r="A9" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="7" t="s">
         <v>62</v>
       </c>
       <c r="C9" s="4">
@@ -1722,7 +1725,7 @@
       <c r="A10" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="4">
@@ -1757,7 +1760,7 @@
       <c r="A11" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C11" s="4">
@@ -1794,7 +1797,7 @@
       <c r="A12" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="7" t="s">
         <v>44</v>
       </c>
       <c r="C12" s="4">
@@ -1833,7 +1836,7 @@
       <c r="A13" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="7" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="4">
@@ -2003,7 +2006,7 @@
       <c r="A2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="4">
@@ -2046,7 +2049,7 @@
       <c r="A3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C3" s="4">
@@ -2089,7 +2092,7 @@
       <c r="A4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C4" s="4">
@@ -2132,7 +2135,7 @@
       <c r="A5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="7" t="s">
         <v>44</v>
       </c>
       <c r="C5" s="4">
@@ -2173,7 +2176,7 @@
       <c r="A6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="4">
@@ -2204,7 +2207,7 @@
       <c r="A7" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C7" s="4">
@@ -2239,7 +2242,7 @@
       <c r="A8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="7" t="s">
         <v>44</v>
       </c>
       <c r="C8" s="4">
@@ -2276,7 +2279,7 @@
       <c r="A9" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="7" t="s">
         <v>62</v>
       </c>
       <c r="C9" s="4">
@@ -2313,7 +2316,7 @@
       <c r="A10" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="4">
@@ -2348,7 +2351,7 @@
       <c r="A11" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C11" s="4">
@@ -2385,7 +2388,7 @@
       <c r="A12" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="7" t="s">
         <v>44</v>
       </c>
       <c r="C12" s="4">
@@ -2424,7 +2427,7 @@
       <c r="A13" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="7" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="4">
